--- a/clean/chemistry/chem_hormones_antibiotics_2025.xlsx
+++ b/clean/chemistry/chem_hormones_antibiotics_2025.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'data'!$A$1:$AP$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'data'!$A$1:$AQ$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP10"/>
+  <dimension ref="A1:AQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -483,9 +483,10 @@
     <col width="26" customWidth="1" min="37" max="37"/>
     <col width="24" customWidth="1" min="38" max="38"/>
     <col width="22" customWidth="1" min="39" max="39"/>
-    <col width="27" customWidth="1" min="40" max="40"/>
-    <col width="24" customWidth="1" min="41" max="41"/>
-    <col width="10" customWidth="1" min="42" max="42"/>
+    <col width="17" customWidth="1" min="40" max="40"/>
+    <col width="27" customWidth="1" min="41" max="41"/>
+    <col width="15" customWidth="1" min="42" max="42"/>
+    <col width="22" customWidth="1" min="43" max="43"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -686,17 +687,22 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>validity_status</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
           <t>sample_category_canonical</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>municipality_canonical</t>
-        </is>
-      </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>sector</t>
+          <t>category_flag</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>sample_name_group</t>
         </is>
       </c>
     </row>
@@ -812,17 +818,17 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
           <t>اللحوم والدواجن</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>الروضة</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>East</t>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>لحم نعيم</t>
         </is>
       </c>
     </row>
@@ -938,17 +944,17 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
           <t>اللحوم والدواجن</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>الروضة</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>East</t>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>لحم روماني</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1070,17 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
           <t>اللحوم والدواجن</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>الروضة</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>East</t>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>لحم عجل</t>
         </is>
       </c>
     </row>
@@ -1187,17 +1193,17 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
           <t>اللحوم والدواجن</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>الروضة</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>East</t>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>دجاج متبل ني</t>
         </is>
       </c>
     </row>
@@ -1313,17 +1319,17 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
           <t>اللحوم والدواجن</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>الروضة</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>East</t>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>لحم ني</t>
         </is>
       </c>
     </row>
@@ -1439,17 +1445,17 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
           <t>اللحوم والدواجن</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>الروضة</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>East</t>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>دجاج ني</t>
         </is>
       </c>
     </row>
@@ -1565,17 +1571,17 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
           <t>اللحوم والدواجن</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>العليا</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>Central</t>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>دجاج متبل ني المراعي</t>
         </is>
       </c>
     </row>
@@ -1691,17 +1697,17 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
           <t>اللحوم والدواجن</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>العليا</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>Central</t>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>كباب لحم</t>
         </is>
       </c>
     </row>
@@ -1817,22 +1823,22 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
           <t>اللحوم والدواجن</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>العليا</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>Central</t>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>أوصال لحم</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP10"/>
+  <autoFilter ref="A1:AQ10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1843,7 +1849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1869,7 +1875,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Columns: 42</t>
+          <t>Columns: 43</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2558,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>sample_category_canonical</t>
+          <t>validity_status</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2563,14 +2569,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>اللحوم والدواجن | اللحوم والدواجن | اللحوم والدواجن</t>
+          <t>valid | valid | valid</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>municipality_canonical</t>
+          <t>sample_category_canonical</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -2581,25 +2587,39 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>الروضة | الروضة | الروضة</t>
+          <t>اللحوم والدواجن | اللحوم والدواجن | اللحوم والدواجن</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>sector</t>
+          <t>category_flag</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>East | East | East</t>
+        <v>9</v>
+      </c>
+      <c r="D47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>sample_name_group</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>9</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>لحم نعيم | لحم روماني | لحم عجل</t>
         </is>
       </c>
     </row>

--- a/clean/chemistry/chem_hormones_antibiotics_2025.xlsx
+++ b/clean/chemistry/chem_hormones_antibiotics_2025.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'data'!$A$1:$AQ$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'data'!$A$1:$AS$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ10"/>
+  <dimension ref="A1:AS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -487,6 +487,8 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="15" customWidth="1" min="42" max="42"/>
     <col width="22" customWidth="1" min="43" max="43"/>
+    <col width="29" customWidth="1" min="44" max="44"/>
+    <col width="13" customWidth="1" min="45" max="45"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -705,6 +707,16 @@
           <t>sample_name_group</t>
         </is>
       </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>sector_flag</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -831,6 +843,11 @@
           <t>لحم نعيم</t>
         </is>
       </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -957,6 +974,11 @@
           <t>لحم روماني</t>
         </is>
       </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1083,6 +1105,11 @@
           <t>لحم عجل</t>
         </is>
       </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1206,6 +1233,11 @@
           <t>دجاج متبل ني</t>
         </is>
       </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1332,6 +1364,11 @@
           <t>لحم ني</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1458,6 +1495,11 @@
           <t>دجاج ني</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1584,6 +1626,11 @@
           <t>دجاج متبل ني المراعي</t>
         </is>
       </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1710,6 +1757,11 @@
           <t>كباب لحم</t>
         </is>
       </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1836,9 +1888,14 @@
           <t>أوصال لحم</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ10"/>
+  <autoFilter ref="A1:AS10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1849,7 +1906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1875,7 +1932,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Columns: 43</t>
+          <t>Columns: 45</t>
         </is>
       </c>
     </row>
@@ -2622,6 +2679,38 @@
           <t>لحم نعيم | لحم روماني | لحم عجل</t>
         </is>
       </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>9</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق | فرع أمانة في الشرق | فرع أمانة في الشرق</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>sector_flag</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" t="n">
+        <v>9</v>
+      </c>
+      <c r="D50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/clean/chemistry/chem_hormones_antibiotics_2025.xlsx
+++ b/clean/chemistry/chem_hormones_antibiotics_2025.xlsx
@@ -1225,7 +1225,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>اللحوم والدواجن</t>
+          <t>الفواكه والخضار</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>اللحوم والدواجن</t>
+          <t>الفواكه والخضار</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>اللحوم والدواجن</t>
+          <t>الفواكه والخضار</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
